--- a/data/trans_bre/P16A10-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A10-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,73</t>
+          <t>-2,69; 2,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,31</t>
+          <t>-1,7; 3,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 3,0</t>
+          <t>-2,38; 3,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,35</t>
+          <t>-2,01; 2,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,54; 39,44</t>
+          <t>-38,9; 46,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 91,08</t>
+          <t>-27,78; 90,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,93; 61,27</t>
+          <t>-31,38; 58,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-25,07; 42,72</t>
+          <t>-25,36; 44,09</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 1,49</t>
+          <t>-2,74; 1,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,14</t>
+          <t>-2,13; 1,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,71</t>
+          <t>-2,62; 1,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,69</t>
+          <t>-0,1; 3,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 31,38</t>
+          <t>-39,66; 34,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,94; 54,59</t>
+          <t>-34,21; 48,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 35,91</t>
+          <t>-39,61; 28,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 195,18</t>
+          <t>-1,64; 192,26</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 2,11</t>
+          <t>-2,92; 1,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,09</t>
+          <t>-3,31; 0,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,89</t>
+          <t>-2,73; 1,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,24; -1,29</t>
+          <t>-6,08; -1,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,83; 50,17</t>
+          <t>-44,28; 44,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-55,39; 36,64</t>
+          <t>-54,61; 29,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 39,95</t>
+          <t>-37,6; 38,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-76,73; -23,93</t>
+          <t>-76,01; -22,87</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,91</t>
+          <t>-1,14; 2,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,55</t>
+          <t>-3,64; 0,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,79</t>
+          <t>-3,43; 0,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,52</t>
+          <t>-3,11; 0,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 77,92</t>
+          <t>-20,52; 72,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,25; 12,46</t>
+          <t>-47,94; 12,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,86; 15,71</t>
+          <t>-49,32; 19,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,22; 9,52</t>
+          <t>-41,98; 12,42</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,0</t>
+          <t>-1,29; 0,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,57</t>
+          <t>-1,5; 0,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,52</t>
+          <t>-1,72; 0,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,78</t>
+          <t>-1,65; 0,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 20,74</t>
+          <t>-21,61; 18,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 12,51</t>
+          <t>-25,38; 14,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 9,55</t>
+          <t>-26,66; 13,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 15,99</t>
+          <t>-27,51; 16,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A10-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A10-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,02</t>
+          <t>-2,81; 2,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 3,36</t>
+          <t>-1,46; 3,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 3,05</t>
+          <t>-2,77; 2,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,46</t>
+          <t>-2,24; 2,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,9; 46,02</t>
+          <t>-40,12; 45,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 90,3</t>
+          <t>-25,49; 89,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 58,02</t>
+          <t>-35,9; 51,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-25,36; 44,09</t>
+          <t>-27,24; 45,0</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 1,68</t>
+          <t>-2,88; 1,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,91</t>
+          <t>-2,08; 1,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,29</t>
+          <t>-2,82; 1,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 3,61</t>
+          <t>-0,9; 2,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 34,44</t>
+          <t>-39,97; 31,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 48,21</t>
+          <t>-34,87; 50,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,61; 28,59</t>
+          <t>-41,41; 30,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 192,26</t>
+          <t>-18,5; 64,38</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,35</t>
+          <t>-2,02</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-50,73%</t>
+          <t>-31,67%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,78</t>
+          <t>-2,92; 1,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,88</t>
+          <t>-3,44; 0,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,88</t>
+          <t>-3,07; 1,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; -1,28</t>
+          <t>-4,17; -0,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,28; 44,72</t>
+          <t>-44,44; 44,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,61; 29,79</t>
+          <t>-56,02; 24,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-37,6; 38,42</t>
+          <t>-40,92; 37,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-76,01; -22,87</t>
+          <t>-53,58; -0,07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-18,44%</t>
+          <t>-11,92%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,83</t>
+          <t>-1,05; 2,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,59</t>
+          <t>-3,78; 0,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,83</t>
+          <t>-3,28; 1,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,69</t>
+          <t>-2,46; 0,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 72,26</t>
+          <t>-20,08; 71,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,94; 12,19</t>
+          <t>-47,97; 8,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,32; 19,01</t>
+          <t>-48,07; 26,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,98; 12,42</t>
+          <t>-32,59; 16,2</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-8,99%</t>
+          <t>-7,86%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,91</t>
+          <t>-1,29; 0,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,68</t>
+          <t>-1,54; 0,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,71</t>
+          <t>-1,74; 0,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,83</t>
+          <t>-1,37; 0,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 18,91</t>
+          <t>-20,98; 18,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 14,87</t>
+          <t>-26,39; 11,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,66; 13,19</t>
+          <t>-26,7; 9,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 16,97</t>
+          <t>-21,32; 8,7</t>
         </is>
       </c>
     </row>
